--- a/isms-core-framework/A.8-technological-controls/isms-a.8.10-data-deletion/WKBK/90_workbooks/ISMS-IMP-A.8.10.4_Verification_Evidence_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.10-data-deletion/WKBK/90_workbooks/ISMS-IMP-A.8.10.4_Verification_Evidence_20260208.xlsx
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Logs capture: How deletion was performed (method reference per NIST SP 800-88)</t>
+          <t>Logs capture: How deletion was performed (method reference per NIST SP 800-88 Rev. 2)</t>
         </is>
       </c>
       <c r="C31" s="6" t="n"/>
@@ -1576,7 +1576,7 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Table 1: Required Log Fields (NIST SP 800-88 R1 Alignment)</t>
+          <t>Table 1: Required Log Fields (NIST SP 800-88 Rev. 2 R1 Alignment)</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>NIST SP 800-88 reference</t>
+          <t>NIST SP 800-88 Rev. 2 reference</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Testing methodology aligns with NIST SP 800-88 R1 verification guidance</t>
+          <t>Testing methodology aligns with NIST SP 800-88 Rev. 2 R1 verification guidance</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Certificates reference deletion method/standard (e.g., NIST SP 800-88)</t>
+          <t>Certificates reference deletion method/standard (e.g., NIST SP 800-88 Rev. 2)</t>
         </is>
       </c>
       <c r="C34" s="6" t="n"/>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>References recognized standard (NIST SP 800-88, GDPR method)</t>
+          <t>References recognized standard (NIST SP 800-88 Rev. 2, GDPR method)</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>NIST SP 800-88 R1 (if applicable)</t>
+          <t>NIST SP 800-88 Rev. 2 R1 (if applicable)</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr"/>
